--- a/data/ams_weekly_data/White_Mulberry/ads_report_week29.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week29.xlsx
@@ -2274,10 +2274,10 @@
         <v>3749</v>
       </c>
       <c r="G66" t="n">
-        <v>1100</v>
+        <v>1633.05</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
